--- a/salida/clinicas_esteticas_sin_web_M30_Madrid.xlsx
+++ b/salida/clinicas_esteticas_sin_web_M30_Madrid.xlsx
@@ -13,8 +13,8 @@
     <sheet name="Metodología y avisos" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads sin web'!$A$1:$N$51</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Descartados (sí tienen web)'!$A$1:$E$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Leads sin web'!$A$1:$N$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Descartados (sí tienen web)'!$A$1:$E$92</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -294,7 +294,7 @@
     <author>Claude</author>
   </authors>
   <commentList>
-    <comment ref="D53" authorId="0" shapeId="0">
+    <comment ref="D57" authorId="0" shapeId="0">
       <text>
         <t>Los recuentos son fórmulas vivas: si borras o añades filas en la tabla, se recalculan solos.</t>
       </text>
@@ -592,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3763,93 +3763,341 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="3" t="inlineStr">
+        <is>
+          <t>Consultas Médicas (Fisioterapia)</t>
+        </is>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>Calle del General Castaños, 13, 2º dcha</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>Justicia</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>913191370 / 675534855</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>eFisioterapia, qdq</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr"/>
+      <c r="K52" s="3" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>Sesión individual de 1 h; bonos de 5, 10 y 30. También a domicilio</t>
+        </is>
+      </c>
+    </row>
     <row r="53">
-      <c r="B53" s="9" t="inlineStr">
+      <c r="A53" s="5" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="6" t="inlineStr">
+        <is>
+          <t>Tu&amp;Fisio — Gabinete de Fisioterapia y Pilates</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Granada, 57, bajo izq.</t>
+        </is>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
+        <is>
+          <t>Pacífico</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>915012035</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I53" s="6" t="inlineStr">
+        <is>
+          <t>eFisioterapia, Fisiosite, Páginas Amarillas</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="inlineStr"/>
+      <c r="K53" s="6" t="inlineStr"/>
+      <c r="L53" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M53" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N53" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia + pilates. Sábados con cita previa</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="3" t="inlineStr">
+        <is>
+          <t>Clínica Ibiza 74</t>
+        </is>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>Calle de Ibiza, 74, 2º E</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>Ibiza</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>Retiro</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>915571190</t>
+        </is>
+      </c>
+      <c r="H54" s="4" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>eFisioterapia</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr"/>
+      <c r="K54" s="3" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia y osteopatía; suelo pélvico, podoactiva, pilates</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>Fisio Juventus</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Gaztambide, 43</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>Gaztambide</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>Chamberí</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>910327161</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>eFisioterapia, Facebook</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr"/>
+      <c r="K55" s="6" t="inlineStr"/>
+      <c r="L55" s="5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="M55" s="5" t="inlineStr">
+        <is>
+          <t>Alta</t>
+        </is>
+      </c>
+      <c r="N55" s="6" t="inlineStr">
+        <is>
+          <t>Solo Facebook como presencia propia</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="9" t="inlineStr">
         <is>
           <t>RESUMEN</t>
         </is>
       </c>
-      <c r="D53" t="n"/>
-    </row>
-    <row r="54">
-      <c r="B54" s="10" t="inlineStr">
-        <is>
-          <t>Total de leads verificados sin web propia</t>
-        </is>
-      </c>
-      <c r="C54" s="11">
-        <f>COUNTA(B2:B51)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>De los cuales, estética / belleza</t>
-        </is>
-      </c>
-      <c r="C55" s="11">
-        <f>COUNTIF(C2:C51,"Estética")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="10" t="inlineStr">
-        <is>
-          <t>De los cuales, clínicas dentales</t>
-        </is>
-      </c>
-      <c r="C56" s="11">
-        <f>COUNTIF(C2:C51,"Dental")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="10" t="inlineStr">
-        <is>
-          <t>De los cuales, fisioterapia</t>
-        </is>
-      </c>
-      <c r="C57" s="11">
-        <f>COUNTIF(C2:C51,"Fisioterapia")</f>
-        <v/>
-      </c>
+      <c r="D57" t="n"/>
     </row>
     <row r="58">
       <c r="B58" s="10" t="inlineStr">
         <is>
-          <t>Fichas con dato de alta fiabilidad</t>
+          <t>Total de leads verificados sin web propia</t>
         </is>
       </c>
       <c r="C58" s="11">
-        <f>COUNTIF(M2:M51,"Alta")</f>
+        <f>COUNTA(B2:B55)</f>
         <v/>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="10" t="inlineStr">
         <is>
-          <t>Fichas a confirmar antes de contactar</t>
+          <t>De los cuales, estética / belleza</t>
         </is>
       </c>
       <c r="C59" s="11">
-        <f>COUNTIF(M2:M51,"Media")</f>
+        <f>COUNTIF(C2:C55,"Estética")</f>
         <v/>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="10" t="inlineStr">
         <is>
+          <t>De los cuales, clínicas dentales</t>
+        </is>
+      </c>
+      <c r="C60" s="11">
+        <f>COUNTIF(C2:C55,"Dental")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="10" t="inlineStr">
+        <is>
+          <t>De los cuales, fisioterapia</t>
+        </is>
+      </c>
+      <c r="C61" s="11">
+        <f>COUNTIF(C2:C55,"Fisioterapia")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="B62" s="10" t="inlineStr">
+        <is>
+          <t>Fichas con dato de alta fiabilidad</t>
+        </is>
+      </c>
+      <c r="C62" s="11">
+        <f>COUNTIF(M2:M55,"Alta")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="10" t="inlineStr">
+        <is>
+          <t>Fichas a confirmar antes de contactar</t>
+        </is>
+      </c>
+      <c r="C63" s="11">
+        <f>COUNTIF(M2:M55,"Media")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="B64" s="10" t="inlineStr">
+        <is>
           <t>Con teléfono directo disponible</t>
         </is>
       </c>
-      <c r="C60" s="11">
-        <f>COUNTA(G2:G51)</f>
+      <c r="C64" s="11">
+        <f>COUNTA(G2:G55)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N51"/>
+  <autoFilter ref="A1:N55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -3861,7 +4109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E74"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5623,26 +5871,576 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="14" t="n">
+        <v>70</v>
+      </c>
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>Centro de Fisioterapia Ana Ramos</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Churruca, 21</t>
+        </is>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>fisioanaramos.com</t>
+        </is>
+      </c>
+    </row>
     <row r="72">
-      <c r="B72" s="10" t="inlineStr">
+      <c r="A72" s="13" t="n">
+        <v>71</v>
+      </c>
+      <c r="B72" s="3" t="inlineStr">
+        <is>
+          <t>Centro de Fisioterapia y Pilates Physios</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>Calle de Valverde, 26</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>centrophysios.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="14" t="n">
+        <v>72</v>
+      </c>
+      <c r="B73" s="6" t="inlineStr">
+        <is>
+          <t>Clínica Fisioterapia y Osteopatía Enric Gallofré</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D73" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Castelló, 24</t>
+        </is>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
+        <is>
+          <t>enricgallofre.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="13" t="n">
+        <v>73</v>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>eFISIO Barrio Salamanca</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>Calle Ruiz Perelló, 3</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="inlineStr">
+        <is>
+          <t>efisio.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="14" t="n">
+        <v>74</v>
+      </c>
+      <c r="B75" s="6" t="inlineStr">
+        <is>
+          <t>MasFisio</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D75" s="6" t="inlineStr">
+        <is>
+          <t>Pasaje del Doctor Esquerdo, 4</t>
+        </is>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
+        <is>
+          <t>masfisio.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="13" t="n">
+        <v>75</v>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>Fisio Moncloa</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>Calle de Cea Bermúdez, 36, 1ºC</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="inlineStr">
+        <is>
+          <t>fisiomoncloa.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="14" t="n">
+        <v>76</v>
+      </c>
+      <c r="B77" s="6" t="inlineStr">
+        <is>
+          <t>Fisioflex Therapy / Fisioflex Salud</t>
+        </is>
+      </c>
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Alberto Aguilera, 64</t>
+        </is>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
+        <is>
+          <t>fisioflexsalud.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>The Clinic Studio</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>Calle de Apodaca, 22</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="inlineStr">
+        <is>
+          <t>theclinicstudio.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="14" t="n">
+        <v>78</v>
+      </c>
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>Clínica Rozalén Goya</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Fernán González, 19</t>
+        </is>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>clinicarozalen.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="13" t="n">
+        <v>79</v>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia y Osteopatía Fuencarral</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>Puerta del Sol, 4, 4ºC</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="inlineStr">
+        <is>
+          <t>fisiofuencarral.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="14" t="n">
+        <v>80</v>
+      </c>
+      <c r="B81" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia Arganzuela (Sanefis)</t>
+        </is>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D81" s="6" t="inlineStr">
+        <is>
+          <t>Calle del Plomo, 15</t>
+        </is>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
+        <is>
+          <t>fisioterapiaarganzuela.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="13" t="n">
+        <v>81</v>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>Fisio Legazpi</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>Calle Jaime el Conquistador, 46</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>fisiolegazpi.eu</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="14" t="n">
+        <v>82</v>
+      </c>
+      <c r="B83" s="6" t="inlineStr">
+        <is>
+          <t>Clínica Bretón de los Herreros</t>
+        </is>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D83" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Bretón de los Herreros, 59</t>
+        </is>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
+        <is>
+          <t>clinicafisioterapiabreton.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="13" t="n">
+        <v>83</v>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia Gaztambide</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>Calle de Gaztambide, 50</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>fisioterapiagaztambide.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="6" t="inlineStr">
+        <is>
+          <t>Atenfis</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D85" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Cristóbal Bordiú, 42</t>
+        </is>
+      </c>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>atenfis.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="13" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>Fisio Axis Retiro</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>Calle de Narciso Serra, 5</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>fisioaxisretiro.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="14" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="6" t="inlineStr">
+        <is>
+          <t>Ciro Rehabilitación</t>
+        </is>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D87" s="6" t="inlineStr">
+        <is>
+          <t>Calle del Doctor Esquerdo, 203</t>
+        </is>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
+        <is>
+          <t>fisioterapiaciro.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="13" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia Ríos</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>Calle de Fernández de los Ríos, 72</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>fisioterapiarios.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="6" t="inlineStr">
+        <is>
+          <t>Clínica de Fisioterapia Marta Mejuto</t>
+        </is>
+      </c>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D89" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Manuel Cortina, 10</t>
+        </is>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
+        <is>
+          <t>clinicamejuto.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="13" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>Fisiotherapy Madrid</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>Calle de Alenza, 20B</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>fisiotherapymadrid.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia SM</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D91" s="6" t="inlineStr">
+        <is>
+          <t>Calle de Covarrubias, 35</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>fisiosmterapia.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="13" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>Clínica EstudioFisio</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Fisioterapia</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>Calle de Viriato, 56</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>estudiofisio.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="10" t="inlineStr">
         <is>
           <t>Total descartados por tener web propia</t>
         </is>
       </c>
-      <c r="C72" s="15">
-        <f>COUNTA(B2:B70)</f>
+      <c r="C94" s="15">
+        <f>COUNTA(B2:B92)</f>
         <v/>
       </c>
     </row>
-    <row r="74">
-      <c r="B74" s="16" t="inlineStr">
+    <row r="96">
+      <c r="B96" s="16" t="inlineStr">
         <is>
           <t>Se listan para que no los vuelvas a prospectar. Todos fueron comprobados uno a uno.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E70"/>
+  <autoFilter ref="A1:E92"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5839,7 +6637,7 @@
     <row r="11">
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>4. Se han verificado uno a uno más de 120 negocios. Los 70 que sí tenían web están en la hoja 'Descartados'.</t>
+          <t>4. Se han verificado uno a uno más de 145 negocios. Los que sí tenían web están en la hoja 'Descartados'.</t>
         </is>
       </c>
     </row>
@@ -5894,7 +6692,7 @@
     <row r="20">
       <c r="B20" s="19" t="inlineStr">
         <is>
-          <t>Dentro de la M-30, las clínicas de fisioterapia y las dentales tienen web propia casi sin excepción: de las 20 verificadas, solo 4 dentales y 0 fisioterapias carecían de web. El nicho real de negocios sin web en esta zona está en la estética y la belleza de barrio, que es donde se concentran 46 de los 50 leads.</t>
+          <t>Dentro de la M-30, la sanidad privada tiene web propia casi sin excepción. Tras un barrido a fondo: de 34 clínicas de fisioterapia verificadas, solo 4 carecen de web propia (un 12%), y una quinta (Fisio Tirso) usa un subdominio gratuito de Webnode. En dental, 4 sin web. El grueso del nicho sigue estando en la estética y la belleza de barrio: 46 de los 54 leads.</t>
         </is>
       </c>
     </row>
